--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -439,110 +439,255 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>record_kind</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>country_code</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>country_name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>disease_id</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>disease_name_en</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>disease_name_zh</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>year_month</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>cases</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>weekly_equiv_cases</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>deaths</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>incidence_rate_per_100k</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>incidence_rate_source</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>mortality_rate</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>series_code</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>source_series_code</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>source_system</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>source_label</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>metric_type</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>reporting_basis</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>temporal_granularity</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>geography_key</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>dimension_key</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>mapping_relation</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>comparability</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>aggregation_policy</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>availability_status</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>missing_value_policy</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>definition_version</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>case_definition</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>case_definition_uri</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>quality_status</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>is_selected_series</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>data_layer</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>projection_policy</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>coverage_status</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>loss_risk</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>selected_series_codes</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>available_series_count</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>provenance_note</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
         <is>
           <t>primary_source_scope</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>primary_source_label</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>primary_source_url</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>primary_source_type</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>source_scopes</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>source_labels</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>source_urls</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source_types</t>
         </is>
@@ -571,97 +716,140 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>D233</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Syphilis over two years or unspecified duration</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>病程超过两年或病程未明的梅毒</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>228</v>
       </c>
-      <c r="N2" t="n">
-        <v>8.76923076923077</v>
-      </c>
       <c r="O2" t="n">
+        <v>228</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>0.8374010948505122</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -690,97 +878,212 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>D233</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Syphilis over two years or unspecified duration</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>病程超过两年或病程未明的梅毒</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>205</v>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
       </c>
       <c r="N3" t="n">
-        <v>47.83333333333333</v>
+        <v>228</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.752926423001557</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+        <v>228</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Syphilis &gt; 2 years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.7</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Australia NINDSS combined category for syphilis over two years duration or unspecified duration.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -809,97 +1112,770 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>D233</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Syphilis over two years or unspecified duration</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>病程超过两年或病程未明的梅毒</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>207</v>
+      </c>
+      <c r="O4" t="n">
+        <v>207</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.7602720466405966</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>syphilis-over-two-years-or-unspecified-duration</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>病程超过两年或病程未明的梅毒</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>207</v>
+      </c>
+      <c r="O5" t="n">
+        <v>207</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Syphilis &gt; 2 years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.7</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Australia NINDSS combined category for syphilis over two years duration or unspecified duration.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>syphilis-over-two-years-or-unspecified-duration</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>病程超过两年或病程未明的梅毒</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="M4" t="n">
-        <v>18</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4.064516129032258</v>
-      </c>
-      <c r="O4" t="n">
+      <c r="N6" t="n">
+        <v>46</v>
+      </c>
+      <c r="O6" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="P4" t="n">
-        <v>0.06611061275135623</v>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R6" t="n">
+        <v>0.1689493436979103</v>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>syphilis-over-two-years-or-unspecified-duration</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>病程超过两年或病程未明的梅毒</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>46</v>
+      </c>
+      <c r="O7" t="n">
+        <v>46</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Syphilis &gt; 2 years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.7</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Australia NINDSS combined category for syphilis over two years duration or unspecified duration.</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -1017,7 +1993,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>record_count</t>
+          <t>projection_record_count</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1027,52 +2003,94 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>schema_version</t>
+          <t>record_count</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>total_cases</t>
+          <t>schema_version</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>451</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>total_deaths</t>
+          <t>source_observation_count</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>window_end</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2029-12-31</t>
-        </is>
+          <t>source_series_count</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>total_basis</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>total_cases</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>total_deaths</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2029-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>window_start</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -760,16 +760,16 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="O2" t="n">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8374010948505122</v>
+        <v>0.855765153948111</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="O3" t="n">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="O6" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1689493436979103</v>
+        <v>0.2203687091711874</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="O7" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>481</v>
+        <v>500</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -760,16 +760,16 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="O2" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.855765153948111</v>
+        <v>0.8704564012261903</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="O3" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1156,16 +1156,16 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="O4" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7602720466405966</v>
+        <v>0.771290482099156</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="O5" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="O6" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2203687091711874</v>
+        <v>0.2497512037273457</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="O7" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>500</v>
+        <v>515</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -1156,16 +1156,16 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="O4" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.771290482099156</v>
+        <v>0.7859817293772351</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="O5" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="O6" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2497512037273457</v>
+        <v>0.2681152628249447</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="O7" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>515</v>
+        <v>524</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>237</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.8704564012261903</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>214</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.7859817293772351</v>
       </c>
@@ -1556,9 +1550,6 @@
       </c>
       <c r="O6" t="n">
         <v>73</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.2681152628249447</v>

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O4" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7859817293772351</v>
+        <v>0.7896545411967548</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O5" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1546,13 +1546,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="O6" t="n">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2681152628249447</v>
+        <v>0.3305530637567811</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="O7" t="n">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>524</v>
+        <v>542</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -760,13 +760,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="O2" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8704564012261903</v>
+        <v>0.8631107775871507</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="O3" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O4" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7896545411967548</v>
+        <v>0.7970001648357945</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O5" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1546,13 +1546,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="O6" t="n">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3305530637567811</v>
+        <v>0.3893180528690977</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="O7" t="n">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>542</v>
+        <v>558</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -760,13 +760,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O2" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8631107775871507</v>
+        <v>0.8667835894066704</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O3" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O4" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7970001648357945</v>
+        <v>0.8006729766553142</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O5" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1546,13 +1546,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="O6" t="n">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3893180528690977</v>
+        <v>0.4554286656204539</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="O7" t="n">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>558</v>
+        <v>578</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN7" t="b">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -760,13 +760,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="O2" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8667835894066704</v>
+        <v>0.8778020248652297</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="O3" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O4" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8006729766553142</v>
+        <v>0.7970001648357945</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O5" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -760,13 +760,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="O2" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8778020248652297</v>
+        <v>0.8851476485042695</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="O3" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O4" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7970001648357945</v>
+        <v>0.8006729766553142</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O5" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>580</v>
+        <v>583</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O4" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8006729766553142</v>
+        <v>0.7933273530162747</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O5" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="O4" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7933273530162747</v>
+        <v>0.8153642239333934</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="O5" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>581</v>
+        <v>587</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O4" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8153642239333934</v>
+        <v>0.8116914121138735</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O5" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -760,13 +760,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O2" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8851476485042695</v>
+        <v>0.8814748366847496</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O3" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O4" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8116914121138735</v>
+        <v>0.8080186002943539</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O5" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -1114,12 +1114,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1144,64 +1144,47 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>220</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.8080186002943539</v>
+        <v>0</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1211,12 +1194,12 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1231,12 +1214,12 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -1268,17 +1251,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1303,139 +1286,47 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>220</v>
+        <v>60</v>
       </c>
       <c r="O5" t="n">
-        <v>220</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Syphilis &gt; 2 years or unspecified duration</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Australia NINDSS combined category for syphilis over two years duration or unspecified duration.</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN5" t="b">
-        <v>1</v>
+        <v>60</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1445,12 +1336,12 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1465,12 +1356,12 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -1507,12 +1398,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1537,64 +1428,47 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>124</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>124</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.4554286656204539</v>
+        <v>5</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1604,12 +1478,12 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1624,12 +1498,12 @@
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -1661,212 +1535,3713 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>病程超过两年或病程未明的梅毒</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>40</v>
+      </c>
+      <c r="O7" t="n">
+        <v>40</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>syphilis-over-two-years-or-unspecified-duration</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>病程超过两年或病程未明的梅毒</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>7</v>
+      </c>
+      <c r="O8" t="n">
+        <v>7</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>syphilis-over-two-years-or-unspecified-duration</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>病程超过两年或病程未明的梅毒</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>syphilis-over-two-years-or-unspecified-duration</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>病程超过两年或病程未明的梅毒</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>86</v>
+      </c>
+      <c r="O10" t="n">
+        <v>86</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>syphilis-over-two-years-or-unspecified-duration</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>病程超过两年或病程未明的梅毒</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>42</v>
+      </c>
+      <c r="O11" t="n">
+        <v>42</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>syphilis-over-two-years-or-unspecified-duration</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>病程超过两年或病程未明的梅毒</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>221</v>
+      </c>
+      <c r="O12" t="n">
+        <v>221</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.8116914121138735</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>syphilis-over-two-years-or-unspecified-duration</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>D233</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Syphilis over two years or unspecified duration</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>病程超过两年或病程未明的梅毒</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>221</v>
+      </c>
+      <c r="O13" t="n">
+        <v>221</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Syphilis &gt; 2 years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Australia NINDSS combined category for syphilis over two years duration or unspecified duration.</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>syphilis-over-two-years-or-unspecified-duration</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>病程超过两年或病程未明的梅毒</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>49</v>
+      </c>
+      <c r="O14" t="n">
+        <v>49</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>syphilis-over-two-years-or-unspecified-duration</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>病程超过两年或病程未明的梅毒</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>9</v>
+      </c>
+      <c r="O15" t="n">
+        <v>9</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>syphilis-over-two-years-or-unspecified-duration</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>病程超过两年或病程未明的梅毒</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>25</v>
+      </c>
+      <c r="O16" t="n">
+        <v>25</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>syphilis-over-two-years-or-unspecified-duration</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>病程超过两年或病程未明的梅毒</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>7</v>
+      </c>
+      <c r="O17" t="n">
+        <v>7</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>syphilis-over-two-years-or-unspecified-duration</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>病程超过两年或病程未明的梅毒</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>93</v>
+      </c>
+      <c r="O18" t="n">
+        <v>93</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>syphilis-over-two-years-or-unspecified-duration</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>病程超过两年或病程未明的梅毒</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>37</v>
+      </c>
+      <c r="O19" t="n">
+        <v>37</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>syphilis-over-two-years-or-unspecified-duration</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>病程超过两年或病程未明的梅毒</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N7" t="n">
+      <c r="N20" t="n">
         <v>124</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O20" t="n">
         <v>124</v>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="R20" t="n">
+        <v>0.4554286656204539</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
         <is>
           <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
         <is>
           <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AT20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>syphilis-over-two-years-or-unspecified-duration</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>病程超过两年或病程未明的梅毒</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>124</v>
+      </c>
+      <c r="O21" t="n">
+        <v>124</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SRC_AU_NINDSS</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>Syphilis &gt; 2 years or unspecified duration</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>notification</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>country:AU:national</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AF21" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG21" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AH21" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AI21" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AJ21" t="inlineStr">
         <is>
           <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr">
+      <c r="AK21" t="inlineStr">
         <is>
           <t>Australia NINDSS combined category for syphilis over two years duration or unspecified duration.</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AM21" t="inlineStr">
         <is>
           <t>provisional; raw</t>
         </is>
       </c>
-      <c r="AN7" t="b">
+      <c r="AN21" t="b">
         <v>1</v>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AO21" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP7" t="inlineStr">
+      <c r="AP21" t="inlineStr">
         <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ7" t="inlineStr">
+      <c r="AQ21" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AS21" t="inlineStr">
         <is>
           <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
         </is>
       </c>
-      <c r="AT7" t="n">
+      <c r="AT21" t="n">
         <v>1</v>
       </c>
-      <c r="AU7" t="inlineStr">
+      <c r="AU21" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX21" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BB21" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>syphilis-over-two-years-or-unspecified-duration</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>病程超过两年或病程未明的梅毒</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>syphilis-over-two-years-or-unspecified-duration</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>病程超过两年或病程未明的梅毒</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>43</v>
+      </c>
+      <c r="O23" t="n">
+        <v>43</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>syphilis-over-two-years-or-unspecified-duration</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>病程超过两年或病程未明的梅毒</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>24</v>
+      </c>
+      <c r="O24" t="n">
+        <v>24</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>syphilis-over-two-years-or-unspecified-duration</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>病程超过两年或病程未明的梅毒</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>5</v>
+      </c>
+      <c r="O25" t="n">
+        <v>5</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>syphilis-over-two-years-or-unspecified-duration</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>病程超过两年或病程未明的梅毒</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>syphilis-over-two-years-or-unspecified-duration</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>病程超过两年或病程未明的梅毒</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>117</v>
+      </c>
+      <c r="O27" t="n">
+        <v>117</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>syphilis-over-two-years-or-unspecified-duration</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>病程超过两年或病程未明的梅毒</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>27</v>
+      </c>
+      <c r="O28" t="n">
+        <v>27</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>syphilis-over-two-years-or-unspecified-duration</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>病程超过两年或病程未明的梅毒</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>13</v>
+      </c>
+      <c r="O29" t="n">
+        <v>13</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.04774655365375727</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>syphilis-over-two-years-or-unspecified-duration</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>病程超过两年或病程未明的梅毒</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>13</v>
+      </c>
+      <c r="O30" t="n">
+        <v>13</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Syphilis &gt; 2 years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Australia NINDSS combined category for syphilis over two years duration or unspecified duration.</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC30" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -1905,7 +5280,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -1988,7 +5363,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -1998,7 +5373,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11">
@@ -2018,7 +5393,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -2050,7 +5425,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>584</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -4921,13 +4921,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="O29" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="R29" t="n">
-        <v>0.04774655365375727</v>
+        <v>0.1028387309465541</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -5080,10 +5080,10 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="O30" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1274</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="16">
